--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>79946</v>
+        <v>80093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,8 +1696,9 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 5929-2022 artfynd.xlsx
+++ b/artfynd/S 5929-2022 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>129721508</v>
       </c>
       <c r="B10" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
